--- a/jogos_2024-11-04.xlsx
+++ b/jogos_2024-11-04.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.88</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="N5" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '44', '59', '65', '69']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45600.33333333334</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.62</v>
+        <v>2.88</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['13', '44', '59', '65', '69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45600.33333333334</v>
@@ -1417,16 +1417,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Radnički Sr. Mitrovica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloboda Užice</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1443,65 +1443,65 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>3.4</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="N8" t="n">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>2.88</v>
       </c>
       <c r="R8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.5</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.44</v>
-      </c>
       <c r="X8" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['59', '72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.6</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.33</v>
+        <v>2.63</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5</v>
+        <v>1.73</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45600.375</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Inđija</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="R9" t="n">
         <v>1.42</v>
@@ -1596,59 +1596,59 @@
         <v>2.65</v>
       </c>
       <c r="T9" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Y9" t="n">
         <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['59', '90']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG9" t="n">
         <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45600.375</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Radnički Sr. Mitrovica</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.4</v>
+        <v>1.57</v>
       </c>
       <c r="M10" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>2.1</v>
+        <v>5.25</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>2.18</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.88</v>
+        <v>5.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>2.19</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>3.8</v>
+        <v>2.81</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="X10" t="n">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.22</v>
+        <v>1.92</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.63</v>
+        <v>1.51</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.73</v>
+        <v>3.02</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45600.375</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Inđija</t>
+          <t>Sloboda Užice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['59', '72']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.33</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['59', '90']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45600.375</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mladost Lučani</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.37</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>4.02</v>
+        <v>1.48</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45600.52083333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Mladost Lučani</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2604,65 +2604,65 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>7</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>3.37</v>
       </c>
       <c r="N17" t="n">
-        <v>1.48</v>
+        <v>4.02</v>
       </c>
       <c r="O17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X17" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.1</v>
-      </c>
       <c r="Y17" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45600.52083333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="N18" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['60', '80']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.5</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI18" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45600.54166666666</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="M19" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S19" t="n">
         <v>3.4</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AC19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['60', '80']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45600.54166666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3120,65 +3120,65 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="M21" t="n">
-        <v>3.88</v>
+        <v>3.56</v>
       </c>
       <c r="N21" t="n">
-        <v>5.13</v>
+        <v>4.13</v>
       </c>
       <c r="O21" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
         <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="Y21" t="n">
         <v>1.88</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AC21" t="n">
         <v>1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['45', '49']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3190,13 +3190,13 @@
         <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45600.58333333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="M22" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>3.2</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['24', '53']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45600.58333333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.25</v>
+        <v>2.52</v>
       </c>
       <c r="M23" t="n">
-        <v>4.33</v>
+        <v>3.08</v>
       </c>
       <c r="N23" t="n">
-        <v>1.45</v>
+        <v>2.83</v>
       </c>
       <c r="O23" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.95</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AC23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['57', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI23" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['27', '42']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['13', '34']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45600.58333333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.57</v>
+        <v>5.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.42</v>
+        <v>4.33</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>1.45</v>
       </c>
       <c r="O24" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.75</v>
+        <v>1.95</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="X24" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.18</v>
+        <v>1.67</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.7</v>
+        <v>2.48</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '42']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '34']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.14</v>
+        <v>2.06</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.82</v>
+        <v>1.13</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45600.58333333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,19 +3610,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -3636,55 +3636,55 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="N25" t="n">
-        <v>1.95</v>
+        <v>5.13</v>
       </c>
       <c r="O25" t="n">
-        <v>4.5</v>
+        <v>2.38</v>
       </c>
       <c r="P25" t="n">
         <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.3</v>
+        <v>4.75</v>
       </c>
       <c r="R25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.29</v>
       </c>
-      <c r="S25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.17</v>
-      </c>
       <c r="X25" t="n">
-        <v>4.5</v>
+        <v>3.44</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>3.33</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AC25" t="n">
         <v>1.8</v>
@@ -3694,25 +3694,25 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>['45', '49']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['55', '90+1', '90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.97</v>
+        <v>1.22</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.62</v>
+        <v>2.88</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45600.58333333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
         <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>4.75</v>
+        <v>1.95</v>
       </c>
       <c r="O26" t="n">
-        <v>2.25</v>
+        <v>4.5</v>
       </c>
       <c r="P26" t="n">
         <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z26" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AA26" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD26" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['9', '67']</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55', '90+1', '90+4']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.14</v>
+        <v>1.97</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.95</v>
+        <v>1.15</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45600.58333333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="M27" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="T27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA27" t="n">
         <v>3.15</v>
       </c>
-      <c r="U27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>4</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['57', '90+3']</t>
+          <t>['24', '53']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="AI27" t="n">
         <v>1.83</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45600.58333333334</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4023,65 +4023,65 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="N28" t="n">
-        <v>4.13</v>
+        <v>4.75</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="P28" t="n">
         <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
         <v>1.05</v>
       </c>
       <c r="W28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.3</v>
       </c>
-      <c r="X28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD28" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['9', '67']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AH28" t="n">
         <v>1.95</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45600.58333333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,19 +4126,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>GOŠK Gabela</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="M29" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="N29" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA29" t="n">
         <v>3.3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.6</v>
       </c>
       <c r="AB29" t="n">
         <v>1.28</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['45+8', '49', '68']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['37', '88']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.66</v>
+        <v>3.14</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45600.58333333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,109 +4255,109 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GOŠK Gabela</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T30" t="n">
         <v>3</v>
       </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M30" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="N30" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R30" t="n">
+      <c r="U30" t="n">
         <v>1.36</v>
       </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="X30" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AB30" t="n">
         <v>1.28</v>
       </c>
       <c r="AC30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>['37', '88']</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>['45+8', '49', '68']</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>['4']</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>5</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45600.58333333334</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,22 +4384,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.97</v>
+        <v>1.56</v>
       </c>
       <c r="M31" t="n">
-        <v>3.48</v>
+        <v>4.01</v>
       </c>
       <c r="N31" t="n">
-        <v>3.73</v>
+        <v>5.08</v>
       </c>
       <c r="O31" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['1', '32']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['79']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45600.60416666666</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,19 +4513,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.95</v>
+        <v>2.74</v>
       </c>
       <c r="M32" t="n">
-        <v>3.66</v>
+        <v>3.13</v>
       </c>
       <c r="N32" t="n">
-        <v>1.58</v>
+        <v>2.67</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="P32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI32" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['90+2']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45600.60416666666</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,109 +4642,109 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z33" t="n">
         <v>2</v>
       </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M33" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="N33" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AA33" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['1', '32']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ33" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45600.60416666666</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,19 +4771,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.74</v>
+        <v>4.95</v>
       </c>
       <c r="M34" t="n">
-        <v>3.13</v>
+        <v>3.66</v>
       </c>
       <c r="N34" t="n">
-        <v>2.67</v>
+        <v>1.58</v>
       </c>
       <c r="O34" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="P34" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="R34" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA34" t="n">
         <v>3.4</v>
       </c>
-      <c r="U34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V34" t="n">
+      <c r="AB34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.08</v>
       </c>
-      <c r="W34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['47']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AI34" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45600.60416666666</v>
@@ -4890,26 +4890,26 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KIF Örebro</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -4926,65 +4926,65 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.06</v>
+        <v>1.66</v>
       </c>
       <c r="M35" t="n">
-        <v>13</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>23</v>
+        <v>4.84</v>
       </c>
       <c r="O35" t="n">
-        <v>1.29</v>
+        <v>2.3</v>
       </c>
       <c r="P35" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="S35" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="U35" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="X35" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="Y35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB35" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AC35" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['5', '16', '64', '74']</t>
+          <t>['6', '14']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AH35" t="n">
-        <v>8.300000000000001</v>
+        <v>2.05</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="AJ35" t="n">
-        <v>8</v>
+        <v>2.88</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45600.625</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,25 +5158,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G37" t="n">
         <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="N37" t="n">
-        <v>4.84</v>
+        <v>7.5</v>
       </c>
       <c r="O37" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="P37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T37" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q37" t="n">
-        <v>5</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>['2', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>['45+3', '90+9']</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH37" t="n">
         <v>2.75</v>
       </c>
-      <c r="U37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>['6', '14']</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AI37" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45600.625</v>
@@ -5277,35 +5277,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>KIF Örebro</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
         <v>2</v>
       </c>
-      <c r="H38" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1</v>
-      </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="M38" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="N38" t="n">
+        <v>23</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>19</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X38" t="n">
         <v>7.5</v>
       </c>
-      <c r="O38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X38" t="n">
-        <v>4.7</v>
-      </c>
       <c r="Y38" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['2', '90+1']</t>
+          <t>['5', '16', '64', '74']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['45+3', '90+9']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.75</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AJ38" t="n">
-        <v>3.75</v>
+        <v>8</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45600.625</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,25 +5803,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,77 +5829,77 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="M42" t="n">
-        <v>3.75</v>
+        <v>4.02</v>
       </c>
       <c r="N42" t="n">
-        <v>4.75</v>
+        <v>5.62</v>
       </c>
       <c r="O42" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="P42" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R42" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="T42" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="U42" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W42" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="X42" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AD42" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['49', '77', '90+3']</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AI42" t="n">
         <v>1.4</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,25 +5932,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N43" t="n">
-        <v>2.63</v>
+        <v>4.75</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="P43" t="n">
         <v>2.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S43" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T43" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="U43" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X43" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['28', '30', '76', '90+6']</t>
+          <t>['49', '77', '90+3']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['47', '63', '71']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45600.66666666666</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,22 +6061,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC44" t="n">
         <v>1.53</v>
       </c>
-      <c r="M44" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="N44" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="O44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD44" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['28', '30', '76', '90+6']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47', '63', '71']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AJ44" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45600.66666666666</v>
@@ -6319,19 +6319,19 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G46" t="n">
         <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
         <v>1</v>
@@ -6345,22 +6345,22 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N46" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="O46" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P46" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
         <v>1.51</v>
@@ -6375,7 +6375,7 @@
         <v>1.33</v>
       </c>
       <c r="V46" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W46" t="n">
         <v>1.4</v>
@@ -6403,25 +6403,25 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['8', '55']</t>
+          <t>['18', '60']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>['39', '50']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45600.6875</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,19 +6448,19 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="M47" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="N47" t="n">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="O47" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S47" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U47" t="n">
         <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W47" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="X47" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="AB47" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC47" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AH47" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AJ47" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45600.6875</v>
@@ -6577,25 +6577,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Turris Neapolis</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="M48" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
       <c r="N48" t="n">
-        <v>3.75</v>
+        <v>12</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="P48" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="R48" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="S48" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="T48" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U48" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="X48" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="Z48" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB48" t="n">
         <v>1.4</v>
       </c>
-      <c r="AA48" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB48" t="n">
+      <c r="AC48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>['22', '53']</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI48" t="n">
         <v>1.17</v>
       </c>
-      <c r="AC48" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>['68']</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ48" t="n">
-        <v>2.75</v>
+        <v>6</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45600.6875</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,25 +6706,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M49" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N49" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="O49" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="R49" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="T49" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U49" t="n">
         <v>1.33</v>
       </c>
       <c r="V49" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W49" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X49" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA49" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AC49" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['18', '60']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>['39', '50']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG49" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI49" t="n">
         <v>1.36</v>
       </c>
-      <c r="AH49" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ49" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45600.6875</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Turris Neapolis</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.22</v>
+        <v>2.63</v>
       </c>
       <c r="M51" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="N51" t="n">
-        <v>12</v>
+        <v>2.63</v>
       </c>
       <c r="O51" t="n">
-        <v>1.67</v>
+        <v>3.4</v>
       </c>
       <c r="P51" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="S51" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="T51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X51" t="n">
         <v>2.88</v>
       </c>
-      <c r="U51" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X51" t="n">
-        <v>4.2</v>
-      </c>
       <c r="Y51" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD51" t="n">
         <v>1.73</v>
       </c>
-      <c r="Z51" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD51" t="n">
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>['8', '55']</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>['18']</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH51" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>['22', '53']</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>['15']</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AI51" t="n">
-        <v>1.17</v>
+        <v>2.05</v>
       </c>
       <c r="AJ51" t="n">
-        <v>6</v>
+        <v>2.05</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45600.6875</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,19 +8512,19 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="G63" t="n">
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -8538,83 +8538,83 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="M63" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N63" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="O63" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P63" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R63" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="S63" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="T63" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="U63" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X63" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z63" t="n">
         <v>1.3</v>
       </c>
-      <c r="V63" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W63" t="n">
+      <c r="AA63" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="AG63" t="n">
         <v>1.42</v>
       </c>
-      <c r="X63" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>['33']</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>['38', '81']</t>
-        </is>
-      </c>
-      <c r="AG63" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH63" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AJ63" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45600.875</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,19 +8641,19 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G64" t="n">
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64" t="n">
         <v>1</v>
@@ -8667,83 +8667,83 @@
         </is>
       </c>
       <c r="L64" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M64" t="n">
         <v>2.9</v>
       </c>
-      <c r="M64" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N64" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="O64" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P64" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X64" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD64" t="n">
         <v>1.73</v>
       </c>
-      <c r="Q64" t="n">
-        <v>4</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S64" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T64" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X64" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>['3']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['38', '81']</t>
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AI64" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45600.875</v>
